--- a/artfynd/A 34616-2026 artfynd.xlsx
+++ b/artfynd/A 34616-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136799694</v>
       </c>
       <c r="B2" t="n">
-        <v>92752</v>
+        <v>92754</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136799884</v>
       </c>
       <c r="B4" t="n">
-        <v>98215</v>
+        <v>98217</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34616-2026 artfynd.xlsx
+++ b/artfynd/A 34616-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136799694</v>
       </c>
       <c r="B2" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136799884</v>
       </c>
       <c r="B4" t="n">
-        <v>98217</v>
+        <v>98223</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34616-2026 artfynd.xlsx
+++ b/artfynd/A 34616-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136799694</v>
       </c>
       <c r="B2" t="n">
-        <v>92756</v>
+        <v>92758</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136799884</v>
       </c>
       <c r="B4" t="n">
-        <v>98223</v>
+        <v>98225</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34616-2026 artfynd.xlsx
+++ b/artfynd/A 34616-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136799694</v>
       </c>
       <c r="B2" t="n">
-        <v>92758</v>
+        <v>92759</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136799884</v>
       </c>
       <c r="B4" t="n">
-        <v>98225</v>
+        <v>98226</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34616-2026 artfynd.xlsx
+++ b/artfynd/A 34616-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136799694</v>
       </c>
       <c r="B2" t="n">
-        <v>92759</v>
+        <v>92765</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136799884</v>
       </c>
       <c r="B4" t="n">
-        <v>98226</v>
+        <v>98232</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34616-2026 artfynd.xlsx
+++ b/artfynd/A 34616-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136799694</v>
       </c>
       <c r="B2" t="n">
-        <v>92765</v>
+        <v>92769</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136799884</v>
       </c>
       <c r="B4" t="n">
-        <v>98232</v>
+        <v>98236</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34616-2026 artfynd.xlsx
+++ b/artfynd/A 34616-2026 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>136799884</v>
       </c>
       <c r="B4" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34616-2026 artfynd.xlsx
+++ b/artfynd/A 34616-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136799694</v>
       </c>
       <c r="B2" t="n">
-        <v>92769</v>
+        <v>92771</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136799884</v>
       </c>
       <c r="B4" t="n">
-        <v>98238</v>
+        <v>98240</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34616-2026 artfynd.xlsx
+++ b/artfynd/A 34616-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136799694</v>
       </c>
       <c r="B2" t="n">
-        <v>92771</v>
+        <v>92784</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136799725</v>
       </c>
       <c r="B3" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136799884</v>
       </c>
       <c r="B4" t="n">
-        <v>98240</v>
+        <v>98253</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34616-2026 artfynd.xlsx
+++ b/artfynd/A 34616-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136799694</v>
       </c>
       <c r="B2" t="n">
-        <v>92784</v>
+        <v>92786</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136799725</v>
       </c>
       <c r="B3" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136799884</v>
       </c>
       <c r="B4" t="n">
-        <v>98253</v>
+        <v>98255</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34616-2026 artfynd.xlsx
+++ b/artfynd/A 34616-2026 artfynd.xlsx
@@ -825,11 +825,7 @@
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>

--- a/artfynd/A 34616-2026 artfynd.xlsx
+++ b/artfynd/A 34616-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136799694</v>
       </c>
       <c r="B2" t="n">
-        <v>92786</v>
+        <v>92789</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136799884</v>
       </c>
       <c r="B4" t="n">
-        <v>98255</v>
+        <v>98258</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34616-2026 artfynd.xlsx
+++ b/artfynd/A 34616-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136799694</v>
       </c>
       <c r="B2" t="n">
-        <v>92789</v>
+        <v>92799</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136799725</v>
       </c>
       <c r="B3" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136799884</v>
       </c>
       <c r="B4" t="n">
-        <v>98258</v>
+        <v>98268</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34616-2026 artfynd.xlsx
+++ b/artfynd/A 34616-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136799694</v>
       </c>
       <c r="B2" t="n">
-        <v>92799</v>
+        <v>92800</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136799884</v>
       </c>
       <c r="B4" t="n">
-        <v>98268</v>
+        <v>98269</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34616-2026 artfynd.xlsx
+++ b/artfynd/A 34616-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136799694</v>
       </c>
       <c r="B2" t="n">
-        <v>92800</v>
+        <v>92803</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136799725</v>
       </c>
       <c r="B3" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136799884</v>
       </c>
       <c r="B4" t="n">
-        <v>98269</v>
+        <v>98274</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34616-2026 artfynd.xlsx
+++ b/artfynd/A 34616-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136799694</v>
       </c>
       <c r="B2" t="n">
-        <v>92803</v>
+        <v>92805</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136799884</v>
       </c>
       <c r="B4" t="n">
-        <v>98274</v>
+        <v>98276</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34616-2026 artfynd.xlsx
+++ b/artfynd/A 34616-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136799694</v>
       </c>
       <c r="B2" t="n">
-        <v>92805</v>
+        <v>92810</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136799725</v>
       </c>
       <c r="B3" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136799884</v>
       </c>
       <c r="B4" t="n">
-        <v>98276</v>
+        <v>98282</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
